--- a/backend/app/resources/typologies/CM.xlsx
+++ b/backend/app/resources/typologies/CM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sagourram\Desktop\Tawazoon-V3\backend\app\resources\typologies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AAA1176-011A-4DB6-B134-EA7B4766E1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC2682E-7598-4AB8-9919-DF37A931FC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$255</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G209" authorId="0" shapeId="0" xr:uid="{46CD47C9-F052-4A12-8A7E-71F10D56CF12}">
+    <comment ref="G207" authorId="0" shapeId="0" xr:uid="{46CD47C9-F052-4A12-8A7E-71F10D56CF12}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="259">
   <si>
     <t>Nom de tâche</t>
   </si>
@@ -604,16 +604,10 @@
     <t xml:space="preserve">Tri Vague master (Cabine de Chargement) </t>
   </si>
   <si>
-    <t xml:space="preserve">Tri Boite Postal (Cabine de Chargement) </t>
-  </si>
-  <si>
     <t xml:space="preserve">Passation CR avec Vague master  </t>
   </si>
   <si>
     <t>Chargement Départ Camions (départ Axes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise CR en Boite Postal  </t>
   </si>
   <si>
     <t>Déchargement Camions ( Arrivée Axes)</t>
@@ -1040,7 +1034,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1089,15 +1083,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1124,13 +1111,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1435,8 +1415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:J255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.88671875" bestFit="1" customWidth="1"/>
@@ -1482,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -1503,7 +1482,7 @@
         <v>125</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I2" s="19">
         <v>7.2333333333333333E-2</v>
@@ -1512,7 +1491,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>129</v>
       </c>
@@ -1533,16 +1512,16 @@
         <v>125</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="32">
+        <v>254</v>
+      </c>
+      <c r="I3" s="29">
         <v>7.3499999999999996E-2</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="29">
         <v>4.41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -1563,7 +1542,7 @@
         <v>125</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I4" s="19">
         <v>6.0499999999999998E-2</v>
@@ -1572,7 +1551,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1580,7 +1559,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="3" t="s">
@@ -1593,14 +1572,14 @@
         <v>36</v>
       </c>
       <c r="H5" s="4"/>
-      <c r="I5" s="32">
+      <c r="I5" s="29">
         <v>6.1166666666666668E-2</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="29">
         <v>3.67</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1608,7 +1587,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="3" t="s">
@@ -1621,14 +1600,14 @@
         <v>36</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="32">
+      <c r="I6" s="29">
         <v>6.1166666666666668E-2</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="29">
         <v>3.67</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>129</v>
       </c>
@@ -1648,7 +1627,7 @@
         <v>125</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I7" s="19">
         <v>7.2333333333333333E-2</v>
@@ -1657,7 +1636,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>130</v>
       </c>
@@ -1678,16 +1657,16 @@
         <v>125</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I8" s="32">
+        <v>254</v>
+      </c>
+      <c r="I8" s="29">
         <v>7.3499999999999996E-2</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="29">
         <v>4.41</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>131</v>
       </c>
@@ -1697,7 +1676,7 @@
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="4" t="s">
         <v>63</v>
       </c>
@@ -1708,7 +1687,7 @@
         <v>125</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I9" s="19">
         <v>0.16666666666666666</v>
@@ -1717,7 +1696,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1725,7 +1704,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="3" t="s">
@@ -1738,14 +1717,14 @@
         <v>36</v>
       </c>
       <c r="H10" s="4"/>
-      <c r="I10" s="32">
+      <c r="I10" s="29">
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="29">
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1753,7 +1732,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="3" t="s">
@@ -1766,14 +1745,14 @@
         <v>36</v>
       </c>
       <c r="H11" s="4"/>
-      <c r="I11" s="32">
+      <c r="I11" s="29">
         <v>3.0000000000000002E-2</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="29">
         <v>1.8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
@@ -1794,7 +1773,7 @@
         <v>125</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I12" s="19">
         <v>6.3166666666666663E-2</v>
@@ -1803,7 +1782,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>133</v>
       </c>
@@ -1821,17 +1800,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H13" s="4"/>
-      <c r="I13" s="32">
+      <c r="I13" s="29">
         <v>7.0833333333333331E-2</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="29">
         <v>4.25</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>134</v>
       </c>
@@ -1849,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="19">
@@ -1859,7 +1838,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1867,7 +1846,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="3" t="s">
@@ -1880,14 +1859,14 @@
         <v>36</v>
       </c>
       <c r="H15" s="4"/>
-      <c r="I15" s="32">
+      <c r="I15" s="29">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="J15" s="32">
+      <c r="J15" s="29">
         <v>1.98</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1895,7 +1874,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="3" t="s">
@@ -1908,14 +1887,14 @@
         <v>36</v>
       </c>
       <c r="H16" s="4"/>
-      <c r="I16" s="32">
+      <c r="I16" s="29">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="J16" s="32">
+      <c r="J16" s="29">
         <v>1.98</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>132</v>
       </c>
@@ -1936,7 +1915,7 @@
         <v>125</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I17" s="19">
         <v>6.3166666666666663E-2</v>
@@ -1945,7 +1924,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>135</v>
       </c>
@@ -1963,17 +1942,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="32">
+      <c r="I18" s="29">
         <v>3.2666666666666663E-2</v>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="29">
         <v>1.96</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>136</v>
       </c>
@@ -1991,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="19">
@@ -2001,7 +1980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
@@ -2009,7 +1988,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="3" t="s">
@@ -2022,14 +2001,14 @@
         <v>36</v>
       </c>
       <c r="H20" s="4"/>
-      <c r="I20" s="32">
+      <c r="I20" s="29">
         <v>6.2000000000000006E-2</v>
       </c>
-      <c r="J20" s="32">
+      <c r="J20" s="29">
         <v>3.72</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
@@ -2037,7 +2016,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="3" t="s">
@@ -2050,14 +2029,14 @@
         <v>36</v>
       </c>
       <c r="H21" s="4"/>
-      <c r="I21" s="32">
+      <c r="I21" s="29">
         <v>6.2000000000000006E-2</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="29">
         <v>3.72</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>137</v>
       </c>
@@ -2075,10 +2054,10 @@
         <v>0.6</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I22" s="19">
         <v>0.128</v>
@@ -2087,8 +2066,8 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
         <v>138</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2105,17 +2084,17 @@
         <v>1</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="32">
+      <c r="I23" s="29">
         <v>7.9333333333333325E-2</v>
       </c>
-      <c r="J23" s="32">
+      <c r="J23" s="29">
         <v>4.76</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>139</v>
       </c>
@@ -2133,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="19">
@@ -2143,7 +2122,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -2151,7 +2130,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="3" t="s">
@@ -2164,14 +2143,14 @@
         <v>36</v>
       </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="32">
+      <c r="I25" s="29">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="29">
         <v>2.76</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -2179,7 +2158,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="s">
@@ -2192,14 +2171,14 @@
         <v>36</v>
       </c>
       <c r="H26" s="4"/>
-      <c r="I26" s="32">
+      <c r="I26" s="29">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="J26" s="32">
+      <c r="J26" s="29">
         <v>2.76</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>140</v>
       </c>
@@ -2217,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="19">
@@ -2227,7 +2206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
@@ -2245,17 +2224,17 @@
         <v>1</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H28" s="4"/>
-      <c r="I28" s="32">
+      <c r="I28" s="29">
         <v>6</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="29">
         <v>360</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>135</v>
       </c>
@@ -2273,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="19">
@@ -2283,7 +2262,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -2291,7 +2270,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="3" t="s">
@@ -2304,14 +2283,14 @@
         <v>36</v>
       </c>
       <c r="H30" s="4"/>
-      <c r="I30" s="32">
+      <c r="I30" s="29">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="29">
         <v>2.76</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>142</v>
       </c>
@@ -2329,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="19">
@@ -2339,7 +2318,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>143</v>
       </c>
@@ -2357,18 +2336,18 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H32" s="4"/>
-      <c r="I32" s="32">
+      <c r="I32" s="29">
         <v>2</v>
       </c>
-      <c r="J32" s="32">
+      <c r="J32" s="29">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="28" t="s">
         <v>144</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -2395,7 +2374,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -2418,14 +2397,14 @@
         <v>36</v>
       </c>
       <c r="H34" s="4"/>
-      <c r="I34" s="32">
+      <c r="I34" s="29">
         <v>2.7678333333333334</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="29">
         <v>166.07</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>69</v>
       </c>
@@ -2443,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="19">
@@ -2453,7 +2432,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>145</v>
       </c>
@@ -2471,21 +2450,21 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H36" s="4"/>
-      <c r="I36" s="32">
-        <v>1</v>
-      </c>
-      <c r="J36" s="32">
+      <c r="I36" s="29">
+        <v>1</v>
+      </c>
+      <c r="J36" s="29">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="26" t="s">
         <v>83</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2499,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="19">
@@ -2509,7 +2488,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>30</v>
       </c>
@@ -2532,14 +2511,14 @@
         <v>36</v>
       </c>
       <c r="H38" s="4"/>
-      <c r="I38" s="32">
+      <c r="I38" s="29">
         <v>2.7678333333333334</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="29">
         <v>166.07</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>31</v>
       </c>
@@ -2560,14 +2539,14 @@
         <v>36</v>
       </c>
       <c r="H39" s="4"/>
-      <c r="I39" s="32">
+      <c r="I39" s="29">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>146</v>
       </c>
@@ -2585,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="19">
@@ -2595,7 +2574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>147</v>
       </c>
@@ -2613,21 +2592,21 @@
         <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H41" s="4"/>
-      <c r="I41" s="32">
+      <c r="I41" s="29">
         <v>2</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="29">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="26" t="s">
         <v>83</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2641,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="19">
@@ -2651,11 +2630,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="26" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -2672,14 +2651,14 @@
         <v>36</v>
       </c>
       <c r="H43" s="4"/>
-      <c r="I43" s="32">
+      <c r="I43" s="29">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="J43" s="32">
+      <c r="J43" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>138</v>
       </c>
@@ -2697,7 +2676,7 @@
         <v>0.4</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="19">
@@ -2707,11 +2686,11 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="26" t="s">
         <v>76</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -2725,17 +2704,17 @@
         <v>1</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H45" s="4"/>
-      <c r="I45" s="32">
+      <c r="I45" s="29">
         <v>0.5</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="29">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>145</v>
       </c>
@@ -2753,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="19">
@@ -2763,7 +2742,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>141</v>
       </c>
@@ -2781,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="19">
@@ -2791,7 +2770,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>149</v>
       </c>
@@ -2809,17 +2788,17 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H48" s="4"/>
-      <c r="I48" s="32">
+      <c r="I48" s="29">
         <v>2</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="29">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>150</v>
       </c>
@@ -2837,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="19">
@@ -2847,7 +2826,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>143</v>
       </c>
@@ -2865,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="19">
@@ -2875,7 +2854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>151</v>
       </c>
@@ -2893,17 +2872,17 @@
         <v>1</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H51" s="4"/>
-      <c r="I51" s="32">
+      <c r="I51" s="29">
         <v>0.13333333333333333</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="29">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>152</v>
       </c>
@@ -2921,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="19">
@@ -2931,7 +2910,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>145</v>
       </c>
@@ -2949,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="19">
@@ -2959,7 +2938,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>153</v>
       </c>
@@ -2977,17 +2956,17 @@
         <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H54" s="4"/>
-      <c r="I54" s="32">
+      <c r="I54" s="29">
         <v>0.128</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="29">
         <v>7.68</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
@@ -3005,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="19">
@@ -3015,7 +2994,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>154</v>
       </c>
@@ -3033,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="19">
@@ -3043,7 +3022,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>155</v>
       </c>
@@ -3064,16 +3043,16 @@
         <v>125</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I57" s="32">
+        <v>254</v>
+      </c>
+      <c r="I57" s="29">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="29">
         <v>5.76</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>148</v>
       </c>
@@ -3091,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="19">
@@ -3101,7 +3080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>156</v>
       </c>
@@ -3119,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="19">
@@ -3129,7 +3108,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>32</v>
       </c>
@@ -3137,7 +3116,7 @@
         <v>75</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="4" t="s">
@@ -3150,14 +3129,14 @@
         <v>36</v>
       </c>
       <c r="H60" s="4"/>
-      <c r="I60" s="32">
+      <c r="I60" s="29">
         <v>3.2666666666666663E-2</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="29">
         <v>1.96</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>157</v>
       </c>
@@ -3175,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="19">
@@ -3185,7 +3164,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>152</v>
       </c>
@@ -3203,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H62" s="15"/>
       <c r="I62" s="19">
@@ -3213,7 +3192,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>158</v>
       </c>
@@ -3221,7 +3200,7 @@
         <v>75</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>77</v>
@@ -3236,14 +3215,14 @@
         <v>36</v>
       </c>
       <c r="H63" s="4"/>
-      <c r="I63" s="32">
+      <c r="I63" s="29">
         <v>3.2666666666666663E-2</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="29">
         <v>1.96</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>149</v>
       </c>
@@ -3261,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="19">
@@ -3271,7 +3250,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>159</v>
       </c>
@@ -3289,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="19">
@@ -3299,7 +3278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>78</v>
       </c>
@@ -3307,7 +3286,7 @@
         <v>75</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>79</v>
@@ -3322,14 +3301,14 @@
         <v>36</v>
       </c>
       <c r="H66" s="4"/>
-      <c r="I66" s="32">
+      <c r="I66" s="29">
         <v>3.2666666666666663E-2</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="29">
         <v>1.96</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>160</v>
       </c>
@@ -3347,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="19">
@@ -3357,7 +3336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>147</v>
       </c>
@@ -3375,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="19">
@@ -3385,7 +3364,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>161</v>
       </c>
@@ -3393,7 +3372,7 @@
         <v>75</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>77</v>
@@ -3408,14 +3387,14 @@
         <v>36</v>
       </c>
       <c r="H69" s="4"/>
-      <c r="I69" s="32">
+      <c r="I69" s="29">
         <v>5.0499999999999996E-2</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="29">
         <v>3.03</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>162</v>
       </c>
@@ -3433,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="19">
@@ -3443,7 +3422,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>148</v>
       </c>
@@ -3461,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="19">
@@ -3471,7 +3450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>80</v>
       </c>
@@ -3479,7 +3458,7 @@
         <v>75</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>79</v>
@@ -3494,14 +3473,14 @@
         <v>36</v>
       </c>
       <c r="H72" s="4"/>
-      <c r="I72" s="32">
+      <c r="I72" s="29">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="J72" s="32">
+      <c r="J72" s="29">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>163</v>
       </c>
@@ -3519,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="19">
@@ -3529,7 +3508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
         <v>157</v>
       </c>
@@ -3547,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="19">
@@ -3557,7 +3536,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>34</v>
       </c>
@@ -3565,10 +3544,10 @@
         <v>75</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>76</v>
@@ -3580,14 +3559,14 @@
         <v>36</v>
       </c>
       <c r="H75" s="4"/>
-      <c r="I75" s="32">
+      <c r="I75" s="29">
         <v>1.4285714285714285E-2</v>
       </c>
-      <c r="J75" s="32">
+      <c r="J75" s="29">
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>164</v>
       </c>
@@ -3608,7 +3587,7 @@
         <v>125</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I76" s="19">
         <v>9.6000000000000002E-2</v>
@@ -3617,7 +3596,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>149</v>
       </c>
@@ -3635,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="19">
@@ -3645,7 +3624,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>35</v>
       </c>
@@ -3653,10 +3632,10 @@
         <v>75</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>76</v>
@@ -3665,19 +3644,19 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I78" s="32">
+      <c r="I78" s="29">
         <v>5.0499999999999996E-2</v>
       </c>
-      <c r="J78" s="32">
+      <c r="J78" s="29">
         <v>3.03</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>165</v>
       </c>
@@ -3685,7 +3664,7 @@
         <v>82</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="4" t="s">
@@ -3695,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="19">
@@ -3705,7 +3684,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>166</v>
       </c>
@@ -3723,7 +3702,7 @@
         <v>0.6</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="19">
@@ -3733,7 +3712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -3741,7 +3720,7 @@
         <v>75</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="4" t="s">
@@ -3754,14 +3733,14 @@
         <v>36</v>
       </c>
       <c r="H81" s="4"/>
-      <c r="I81" s="32">
+      <c r="I81" s="29">
         <v>3.2666666666666663E-2</v>
       </c>
-      <c r="J81" s="32">
+      <c r="J81" s="29">
         <v>1.96</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>167</v>
       </c>
@@ -3769,7 +3748,7 @@
         <v>82</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="4" t="s">
@@ -3779,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="19">
@@ -3789,7 +3768,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>166</v>
       </c>
@@ -3807,7 +3786,7 @@
         <v>0.4</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="19">
@@ -3817,7 +3796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>37</v>
       </c>
@@ -3825,7 +3804,7 @@
         <v>75</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="4" t="s">
@@ -3838,14 +3817,14 @@
         <v>36</v>
       </c>
       <c r="H84" s="4"/>
-      <c r="I84" s="32">
+      <c r="I84" s="29">
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="J84" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J84" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>168</v>
       </c>
@@ -3853,7 +3832,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="4" t="s">
@@ -3873,7 +3852,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>153</v>
       </c>
@@ -3891,7 +3870,7 @@
         <v>0.6</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" s="19">
@@ -3901,7 +3880,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>38</v>
       </c>
@@ -3909,7 +3888,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="4" t="s">
@@ -3922,14 +3901,14 @@
         <v>36</v>
       </c>
       <c r="H87" s="4"/>
-      <c r="I87" s="32">
+      <c r="I87" s="29">
         <v>0.10016666666666667</v>
       </c>
-      <c r="J87" s="32">
+      <c r="J87" s="29">
         <v>6.01</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>169</v>
       </c>
@@ -3937,7 +3916,7 @@
         <v>82</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>77</v>
@@ -3959,7 +3938,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>163</v>
       </c>
@@ -3977,7 +3956,7 @@
         <v>0.4</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="19">
@@ -3987,7 +3966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>39</v>
       </c>
@@ -4010,84 +3989,84 @@
         <v>36</v>
       </c>
       <c r="H90" s="4"/>
-      <c r="I90" s="32">
+      <c r="I90" s="29">
         <v>0.37416666666666665</v>
       </c>
-      <c r="J90" s="32">
+      <c r="J90" s="29">
         <v>22.45</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="B91" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D91" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="E91" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F91" s="23">
-        <v>1</v>
-      </c>
-      <c r="G91" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H91" s="22"/>
-      <c r="I91" s="34">
-        <v>3.7666666666666661E-2</v>
-      </c>
-      <c r="J91" s="35">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="B91" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="5"/>
+      <c r="E91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F91" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H91" s="4"/>
+      <c r="I91" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="J91" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="B92" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F92" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>256</v>
+        <v>1</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H92" s="4"/>
-      <c r="I92" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="J92" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>75</v>
+      <c r="I92" s="29">
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="J92" s="29">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D93" s="5"/>
+        <v>249</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="E93" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F93" s="10">
         <v>1</v>
@@ -4096,1170 +4075,1172 @@
         <v>36</v>
       </c>
       <c r="H93" s="4"/>
-      <c r="I93" s="32">
-        <v>6.6666666666666671E-3</v>
-      </c>
-      <c r="J93" s="32">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I93" s="19">
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="J93" s="18">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="5"/>
+      <c r="E94" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I94" s="19">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="J94" s="18">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F95" s="10">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H95" s="4"/>
+      <c r="I95" s="29">
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="J95" s="29">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="5"/>
+      <c r="E96" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F96" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I96" s="19">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="J96" s="18">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" s="5"/>
+      <c r="E97" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F97" s="10">
+        <v>1</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I97" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J97" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F94" s="10">
-        <v>1</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H94" s="4"/>
-      <c r="I94" s="19">
-        <v>5.0499999999999996E-2</v>
-      </c>
-      <c r="J94" s="18">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F95" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I95" s="19">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="J95" s="18">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F96" s="10">
-        <v>1</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H96" s="4"/>
-      <c r="I96" s="32">
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="J96" s="32">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C97" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D97" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="E97" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F97" s="23">
-        <v>1</v>
-      </c>
-      <c r="G97" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H97" s="22"/>
-      <c r="I97" s="34">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="J97" s="37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B98" s="21" t="s">
-        <v>73</v>
-      </c>
       <c r="C98" s="4" t="s">
-        <v>23</v>
+        <v>249</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F98" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>256</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H98" s="4"/>
       <c r="I98" s="19">
-        <v>9.6000000000000002E-2</v>
+        <v>1.9333333333333331E-2</v>
       </c>
       <c r="J98" s="18">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B99" s="21" t="s">
-        <v>88</v>
+      <c r="B99" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>42</v>
+        <v>249</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F99" s="10">
         <v>1</v>
       </c>
-      <c r="G99" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I99" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J99" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G99" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H99" s="4"/>
+      <c r="I99" s="19">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J99" s="18">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>82</v>
+      <c r="B100" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>251</v>
+        <v>42</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F100" s="10">
         <v>1</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H100" s="4"/>
-      <c r="I100" s="19">
-        <v>1.9333333333333331E-2</v>
-      </c>
-      <c r="J100" s="18">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I100" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J100" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>81</v>
+      <c r="B101" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F101" s="10">
         <v>1</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H101" s="4"/>
+      <c r="G101" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="I101" s="19">
-        <v>5.1833333333333328E-2</v>
+        <v>5.0499999999999996E-2</v>
       </c>
       <c r="J101" s="18">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B102" s="17" t="s">
-        <v>88</v>
+        <v>167</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>42</v>
+        <v>249</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F102" s="10">
         <v>1</v>
       </c>
-      <c r="G102" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I102" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J102" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G102" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H102" s="4"/>
+      <c r="I102" s="19">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="J102" s="18">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B103" s="24" t="s">
-        <v>82</v>
+        <v>177</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>251</v>
+        <v>42</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F103" s="10">
         <v>1</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I103" s="19">
-        <v>5.0499999999999996E-2</v>
-      </c>
-      <c r="J103" s="18">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="I103" s="29">
+        <v>0.128</v>
+      </c>
+      <c r="J103" s="29">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>81</v>
+        <v>178</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F104" s="10">
         <v>1</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>256</v>
+      <c r="G104" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="19">
-        <v>5.9499999999999997E-2</v>
+        <v>3.7666666666666661E-2</v>
       </c>
       <c r="J104" s="18">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>88</v>
+      <c r="B105" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>42</v>
+        <v>249</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F105" s="10">
         <v>1</v>
       </c>
-      <c r="G105" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I105" s="32">
-        <v>0.128</v>
-      </c>
-      <c r="J105" s="32">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G105" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H105" s="4"/>
+      <c r="I105" s="19">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="J105" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B106" s="24" t="s">
-        <v>82</v>
+      <c r="B106" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F106" s="10">
         <v>1</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="H106" s="4"/>
-      <c r="I106" s="19">
-        <v>3.7666666666666661E-2</v>
-      </c>
-      <c r="J106" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I106" s="29">
+        <v>3.2666666666666663E-2</v>
+      </c>
+      <c r="J106" s="29">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>81</v>
+      <c r="B107" s="17" t="s">
+        <v>82</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="4" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F107" s="10">
         <v>1</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>256</v>
+      <c r="G107" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="19">
-        <v>1.6666666666666666E-2</v>
-      </c>
-      <c r="J107" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="J107" s="18">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>88</v>
+      <c r="B108" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>65</v>
+        <v>249</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F108" s="10">
         <v>1</v>
       </c>
-      <c r="G108" s="4" t="s">
-        <v>256</v>
+      <c r="G108" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="H108" s="4"/>
-      <c r="I108" s="32">
-        <v>3.2666666666666663E-2</v>
-      </c>
-      <c r="J108" s="32">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I108" s="19">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J108" s="18">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>82</v>
+        <v>186</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>76</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>251</v>
+        <v>42</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="4" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F109" s="10">
         <v>1</v>
       </c>
-      <c r="G109" s="4" t="s">
-        <v>36</v>
+      <c r="G109" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H109" s="4"/>
-      <c r="I109" s="19">
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="J109" s="18">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I109" s="29">
+        <v>6</v>
+      </c>
+      <c r="J109" s="29">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B110" s="14" t="s">
-        <v>81</v>
+      <c r="B110" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F110" s="10">
         <v>1</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>84</v>
+      <c r="G110" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="19">
-        <v>5.1833333333333328E-2</v>
-      </c>
-      <c r="J110" s="18">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B111" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D111" s="8"/>
+      <c r="E111" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F111" s="10">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H111" s="4"/>
+      <c r="I111" s="19">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="J111" s="18">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D111" s="5"/>
-      <c r="E111" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F111" s="10">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H111" s="4"/>
-      <c r="I111" s="32">
-        <v>6</v>
-      </c>
-      <c r="J111" s="32">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D112" s="5"/>
-      <c r="E112" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F112" s="10">
         <v>1</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="H112" s="4"/>
-      <c r="I112" s="19">
-        <v>1.6666666666666666E-2</v>
-      </c>
-      <c r="J112" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I112" s="29">
+        <v>0.37416666666666665</v>
+      </c>
+      <c r="J112" s="29">
+        <v>22.45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B113" s="29" t="s">
-        <v>81</v>
+      <c r="B113" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D113" s="8"/>
+        <v>249</v>
+      </c>
+      <c r="D113" s="5"/>
       <c r="E113" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F113" s="10">
         <v>1</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>84</v>
+      <c r="G113" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="19">
-        <v>5.2499999999999998E-2</v>
+        <v>0.10016666666666667</v>
       </c>
       <c r="J113" s="18">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B114" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D114" s="5"/>
+      <c r="E114" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F114" s="10">
+        <v>1</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I114" s="19">
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="J114" s="18">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E114" s="4" t="s">
+      <c r="C115" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E115" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F114" s="10">
-        <v>1</v>
-      </c>
-      <c r="G114" s="4" t="s">
+      <c r="F115" s="10">
+        <v>1</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H114" s="4"/>
-      <c r="I114" s="32">
-        <v>0.37416666666666665</v>
-      </c>
-      <c r="J114" s="32">
-        <v>22.45</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+      <c r="H115" s="4"/>
+      <c r="I115" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J115" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B116" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D115" s="5"/>
-      <c r="E115" s="4" t="s">
+      <c r="C116" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F115" s="10">
-        <v>1</v>
-      </c>
-      <c r="G115" s="4" t="s">
+      <c r="F116" s="10">
+        <v>1</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H115" s="4"/>
-      <c r="I115" s="19">
-        <v>0.10016666666666667</v>
-      </c>
-      <c r="J115" s="18">
-        <v>6.01</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B116" s="3" t="s">
+      <c r="H116" s="4"/>
+      <c r="I116" s="19">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="J116" s="18">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D116" s="5"/>
-      <c r="E116" s="4" t="s">
+      <c r="C117" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D117" s="5"/>
+      <c r="E117" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F116" s="10">
-        <v>1</v>
-      </c>
-      <c r="G116" s="4" t="s">
+      <c r="F117" s="10">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H116" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I116" s="19">
-        <v>5.0499999999999996E-2</v>
-      </c>
-      <c r="J116" s="18">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F117" s="10">
-        <v>1</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="H117" s="4"/>
-      <c r="I117" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J117" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I117" s="19">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J117" s="18">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B118" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" s="10">
+        <v>1</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I118" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J118" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C119" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E118" s="4" t="s">
+      <c r="D119" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E119" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F118" s="10">
-        <v>1</v>
-      </c>
-      <c r="G118" s="4" t="s">
+      <c r="F119" s="10">
+        <v>1</v>
+      </c>
+      <c r="G119" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="H118" s="4"/>
-      <c r="I118" s="19">
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="J118" s="18">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D119" s="5"/>
-      <c r="E119" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F119" s="10">
-        <v>1</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="H119" s="4"/>
       <c r="I119" s="19">
-        <v>5.1833333333333328E-2</v>
+        <v>2.7678333333333334</v>
       </c>
       <c r="J119" s="18">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>166.07</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>95</v>
+        <v>181</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>104</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="D120" s="5"/>
       <c r="E120" s="4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F120" s="10">
         <v>1</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I120" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J120" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="H120" s="4"/>
+      <c r="I120" s="19">
+        <v>3.0000000000000002E-2</v>
+      </c>
+      <c r="J120" s="18">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>192</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F121" s="10">
+        <v>1</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H121" s="4"/>
+      <c r="I121" s="29">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="J121" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F122" s="10">
+        <v>1</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H122" s="4"/>
+      <c r="I122" s="29">
+        <v>3.2666666666666663E-2</v>
+      </c>
+      <c r="J122" s="29">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B123" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E121" s="4" t="s">
+      <c r="C123" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D123" s="5"/>
+      <c r="E123" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F121" s="10">
-        <v>1</v>
-      </c>
-      <c r="G121" s="4" t="s">
+      <c r="F123" s="10">
+        <v>1</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H121" s="4"/>
-      <c r="I121" s="19">
-        <v>2.7678333333333334</v>
-      </c>
-      <c r="J121" s="18">
-        <v>166.07</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B122" s="3" t="s">
+      <c r="H123" s="4"/>
+      <c r="I123" s="19">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="J123" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B124" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D122" s="5"/>
-      <c r="E122" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F122" s="10">
-        <v>1</v>
-      </c>
-      <c r="G122" s="3" t="s">
+      <c r="C124" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F124" s="10">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H122" s="4"/>
-      <c r="I122" s="19">
-        <v>3.0000000000000002E-2</v>
-      </c>
-      <c r="J122" s="18">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+      <c r="H124" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I124" s="19">
+        <v>0.10016666666666667</v>
+      </c>
+      <c r="J124" s="18">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F125" s="10">
+        <v>1</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H125" s="4"/>
+      <c r="I125" s="29">
+        <v>0.37416666666666665</v>
+      </c>
+      <c r="J125" s="29">
+        <v>22.45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F123" s="10">
-        <v>1</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H123" s="4"/>
-      <c r="I123" s="32">
-        <v>8.3333333333333332E-3</v>
-      </c>
-      <c r="J123" s="32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+      <c r="B126" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F126" s="10">
+        <v>1</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I126" s="19">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J126" s="18">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B124" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F124" s="10">
-        <v>1</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="H124" s="4"/>
-      <c r="I124" s="32">
-        <v>3.2666666666666663E-2</v>
-      </c>
-      <c r="J124" s="32">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B125" s="29" t="s">
+      <c r="B127" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D125" s="5"/>
-      <c r="E125" s="4" t="s">
+      <c r="C127" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E127" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F125" s="10">
-        <v>1</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H125" s="4"/>
-      <c r="I125" s="19">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="J125" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B126" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D126" s="8"/>
-      <c r="E126" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F126" s="10">
-        <v>1</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I126" s="19">
-        <v>0.10016666666666667</v>
-      </c>
-      <c r="J126" s="18">
-        <v>6.01</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="F127" s="10">
         <v>1</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="H127" s="4"/>
-      <c r="I127" s="32">
-        <v>0.37416666666666665</v>
-      </c>
-      <c r="J127" s="32">
-        <v>22.45</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I127" s="19">
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="J127" s="9">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D128" s="5"/>
+      <c r="E128" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F128" s="10">
+        <v>1</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I128" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="J128" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F129" s="10">
+        <v>1</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H129" s="4"/>
+      <c r="I129" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J129" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B130" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E128" s="4" t="s">
+      <c r="C130" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F128" s="10">
-        <v>1</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I128" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J128" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F129" s="10">
-        <v>1</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H129" s="4"/>
-      <c r="I129" s="19">
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="J129" s="9">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B130" s="29" t="s">
+      <c r="F130" s="10">
+        <v>1</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H130" s="4"/>
+      <c r="I130" s="19">
+        <v>1.9333333333333331E-2</v>
+      </c>
+      <c r="J130" s="18">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B131" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C130" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D130" s="5"/>
-      <c r="E130" s="4" t="s">
+      <c r="C131" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D131" s="5"/>
+      <c r="E131" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F130" s="10">
-        <v>1</v>
-      </c>
-      <c r="G130" s="3" t="s">
+      <c r="F131" s="10">
+        <v>1</v>
+      </c>
+      <c r="G131" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H130" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I130" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="J130" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F131" s="10">
-        <v>1</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="H131" s="4"/>
-      <c r="I131" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J131" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I131" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="J131" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B132" s="30" t="s">
+      <c r="B132" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F132" s="10">
+        <v>1</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I132" s="29">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J132" s="29">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C132" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D132" s="5" t="s">
+      <c r="C133" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E133" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F132" s="10">
-        <v>1</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H132" s="4"/>
-      <c r="I132" s="19">
-        <v>1.9333333333333331E-2</v>
-      </c>
-      <c r="J132" s="18">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B133" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D133" s="5"/>
-      <c r="E133" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="F133" s="10">
         <v>1</v>
@@ -5269,59 +5250,57 @@
       </c>
       <c r="H133" s="4"/>
       <c r="I133" s="19">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J133" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B134" s="29" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F134" s="10">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I134" s="32">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J134" s="32">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="H134" s="4"/>
+      <c r="I134" s="19">
+        <v>1.6333333333333333</v>
+      </c>
+      <c r="J134" s="18">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>200</v>
+        <v>93</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F135" s="10">
         <v>1</v>
@@ -5331,241 +5310,241 @@
       </c>
       <c r="H135" s="4"/>
       <c r="I135" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="J135" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.45</v>
+      </c>
+      <c r="J135" s="18">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F136" s="10">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H136" s="4"/>
+      <c r="I136" s="29">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="J136" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F137" s="10">
+        <v>1</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H137" s="4"/>
+      <c r="I137" s="29">
+        <v>3.2666666666666663E-2</v>
+      </c>
+      <c r="J137" s="29">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F138" s="10">
+        <v>1</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H138" s="4"/>
+      <c r="I138" s="19">
+        <v>1.9333333333333331E-2</v>
+      </c>
+      <c r="J138" s="18">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B139" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C136" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E136" s="4" t="s">
+      <c r="C139" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E139" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F136" s="10">
-        <v>1</v>
-      </c>
-      <c r="G136" s="3" t="s">
+      <c r="F139" s="10">
+        <v>1</v>
+      </c>
+      <c r="G139" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H136" s="4"/>
-      <c r="I136" s="19">
-        <v>1.6333333333333333</v>
-      </c>
-      <c r="J136" s="18">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F137" s="10">
-        <v>1</v>
-      </c>
-      <c r="G137" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H137" s="4"/>
-      <c r="I137" s="19">
-        <v>3.45</v>
-      </c>
-      <c r="J137" s="18">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B138" s="3" t="s">
+      <c r="H139" s="4"/>
+      <c r="I139" s="19">
+        <v>7.2333333333333333E-2</v>
+      </c>
+      <c r="J139" s="18">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E138" s="4" t="s">
+      <c r="C140" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E140" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F138" s="10">
-        <v>1</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H138" s="4"/>
-      <c r="I138" s="32">
-        <v>8.3333333333333332E-3</v>
-      </c>
-      <c r="J138" s="32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F139" s="10">
-        <v>1</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="H139" s="4"/>
-      <c r="I139" s="32">
-        <v>3.2666666666666663E-2</v>
-      </c>
-      <c r="J139" s="32">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F140" s="10">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="H140" s="4"/>
-      <c r="I140" s="19">
-        <v>1.9333333333333331E-2</v>
-      </c>
-      <c r="J140" s="18">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I140" s="29">
+        <v>1.2273333333333334</v>
+      </c>
+      <c r="J140" s="29">
+        <v>73.64</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>92</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="D141" s="5"/>
       <c r="E141" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F141" s="10">
         <v>1</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>84</v>
+      <c r="G141" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="19">
-        <v>7.2333333333333333E-2</v>
-      </c>
-      <c r="J141" s="18">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="J141" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>255</v>
+        <v>127</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F142" s="10">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H142" s="4"/>
-      <c r="I142" s="32">
-        <v>1.2273333333333334</v>
-      </c>
-      <c r="J142" s="32">
-        <v>73.64</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I142" s="19">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J142" s="18">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F143" s="10">
         <v>1</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="H143" s="4"/>
       <c r="I143" s="19">
@@ -5576,135 +5555,133 @@
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>196</v>
+      <c r="A144" s="22" t="s">
+        <v>205</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>127</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D144" s="5"/>
       <c r="E144" s="4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F144" s="10">
         <v>1</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I144" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J144" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G144" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H144" s="4"/>
+      <c r="I144" s="29">
+        <v>7.9333333333333325E-2</v>
+      </c>
+      <c r="J144" s="29">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D145" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="E145" s="4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F145" s="10">
         <v>1</v>
       </c>
-      <c r="G145" s="4" t="s">
-        <v>84</v>
+      <c r="G145" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H145" s="4"/>
       <c r="I145" s="19">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="J145" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="25" t="s">
-        <v>207</v>
+        <v>3.2666666666666663E-2</v>
+      </c>
+      <c r="J145" s="18">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="C146" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F146" s="10">
+        <v>1</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H146" s="4"/>
+      <c r="I146" s="29">
+        <v>2.7678333333333334</v>
+      </c>
+      <c r="J146" s="29">
+        <v>166.07</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D146" s="5"/>
-      <c r="E146" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F146" s="10">
-        <v>1</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H146" s="4"/>
-      <c r="I146" s="32">
-        <v>7.9333333333333325E-2</v>
-      </c>
-      <c r="J146" s="32">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>96</v>
-      </c>
+      <c r="D147" s="5"/>
       <c r="E147" s="4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F147" s="10">
         <v>1</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H147" s="4"/>
       <c r="I147" s="19">
-        <v>3.2666666666666663E-2</v>
+        <v>6</v>
       </c>
       <c r="J147" s="18">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>83</v>
@@ -5716,938 +5693,940 @@
         <v>101</v>
       </c>
       <c r="H148" s="4"/>
-      <c r="I148" s="32">
-        <v>2.7678333333333334</v>
-      </c>
-      <c r="J148" s="32">
-        <v>166.07</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I148" s="19">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="J148" s="9">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F149" s="10">
+        <v>1</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I149" s="29">
+        <v>9.0000000000000011E-2</v>
+      </c>
+      <c r="J149" s="29">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C150" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D149" s="5"/>
-      <c r="E149" s="4" t="s">
+      <c r="D150" s="5"/>
+      <c r="E150" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F149" s="10">
-        <v>1</v>
-      </c>
-      <c r="G149" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H149" s="4"/>
-      <c r="I149" s="19">
-        <v>6</v>
-      </c>
-      <c r="J149" s="18">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F150" s="10">
         <v>1</v>
       </c>
-      <c r="G150" s="4" t="s">
-        <v>101</v>
+      <c r="G150" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" s="19">
-        <v>6.0499999999999998E-2</v>
-      </c>
-      <c r="J150" s="9">
-        <v>3.63</v>
+        <v>2</v>
+      </c>
+      <c r="J150" s="18">
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>40</v>
+        <v>258</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F151" s="10">
         <v>1</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>256</v>
+      <c r="G151" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I151" s="32">
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="J151" s="32">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="I151" s="19">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J151" s="18">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>209</v>
+        <v>105</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D152" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="E152" s="4" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F152" s="10">
         <v>1</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>256</v>
+      <c r="G152" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="19">
-        <v>2</v>
-      </c>
-      <c r="J152" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.5666666666666666E-2</v>
+      </c>
+      <c r="J152" s="9">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>65</v>
+        <v>249</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F153" s="10">
         <v>1</v>
       </c>
-      <c r="G153" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I153" s="19">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J153" s="18">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G153" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H153" s="4"/>
+      <c r="I153" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="J153" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>104</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D154" s="5"/>
       <c r="E154" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F154" s="10">
         <v>1</v>
       </c>
-      <c r="G154" s="4" t="s">
-        <v>256</v>
+      <c r="G154" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H154" s="4"/>
       <c r="I154" s="19">
-        <v>3.5666666666666666E-2</v>
-      </c>
-      <c r="J154" s="9">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J154" s="18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F155" s="10">
+        <v>1</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H155" s="4"/>
+      <c r="I155" s="19">
+        <v>7.85E-2</v>
+      </c>
+      <c r="J155" s="18">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F156" s="10">
+        <v>1</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H156" s="4"/>
+      <c r="I156" s="29">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="J156" s="29">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B155" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F155" s="10">
-        <v>1</v>
-      </c>
-      <c r="G155" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H155" s="4"/>
-      <c r="I155" s="32">
-        <v>0.1</v>
-      </c>
-      <c r="J155" s="32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B156" s="3" t="s">
+      <c r="B157" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C157" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D156" s="5"/>
-      <c r="E156" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F156" s="10">
-        <v>1</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H156" s="4"/>
-      <c r="I156" s="19">
-        <v>1</v>
-      </c>
-      <c r="J156" s="18">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="D157" s="5"/>
       <c r="E157" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F157" s="10">
         <v>1</v>
       </c>
-      <c r="G157" s="4" t="s">
-        <v>256</v>
+      <c r="G157" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H157" s="4"/>
       <c r="I157" s="19">
-        <v>7.85E-2</v>
+        <v>2</v>
       </c>
       <c r="J157" s="18">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>203</v>
+        <v>54</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E158" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F158" s="10">
+        <v>1</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H158" s="4"/>
+      <c r="I158" s="19">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J158" s="18">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E159" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F158" s="10">
-        <v>1</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H158" s="4"/>
-      <c r="I158" s="32">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="J158" s="32">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B159" s="3" t="s">
+      <c r="F159" s="10">
+        <v>1</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H159" s="4"/>
+      <c r="I159" s="29">
+        <v>1.6333333333333333</v>
+      </c>
+      <c r="J159" s="29">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B160" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C160" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D159" s="5"/>
-      <c r="E159" s="4" t="s">
+      <c r="D160" s="5"/>
+      <c r="E160" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F159" s="10">
-        <v>1</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H159" s="4"/>
-      <c r="I159" s="19">
-        <v>2</v>
-      </c>
-      <c r="J159" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F160" s="10">
         <v>1</v>
       </c>
-      <c r="G160" s="4" t="s">
-        <v>256</v>
+      <c r="G160" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H160" s="4"/>
       <c r="I160" s="19">
-        <v>0.10483333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="J160" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F161" s="10">
+        <v>1</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H161" s="4"/>
+      <c r="I161" s="19">
+        <v>3.7666666666666661E-2</v>
+      </c>
+      <c r="J161" s="18">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B162" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E161" s="4" t="s">
+      <c r="C162" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E162" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F161" s="10">
-        <v>1</v>
-      </c>
-      <c r="G161" s="4" t="s">
+      <c r="F162" s="10">
+        <v>1</v>
+      </c>
+      <c r="G162" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H161" s="4"/>
-      <c r="I161" s="32">
-        <v>1.6333333333333333</v>
-      </c>
-      <c r="J161" s="32">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
+      <c r="H162" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I162" s="29">
+        <v>7.2333333333333333E-2</v>
+      </c>
+      <c r="J162" s="29">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B162" s="29" t="s">
+      <c r="B163" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C163" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D162" s="5"/>
-      <c r="E162" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F162" s="10">
-        <v>1</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H162" s="4"/>
-      <c r="I162" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="J162" s="18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="D163" s="5"/>
       <c r="E163" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F163" s="10">
         <v>1</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H163" s="4"/>
       <c r="I163" s="19">
-        <v>3.7666666666666661E-2</v>
+        <v>2</v>
       </c>
       <c r="J163" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F164" s="10">
+        <v>1</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H164" s="4"/>
+      <c r="I164" s="19">
+        <v>2.7678333333333334</v>
+      </c>
+      <c r="J164" s="18">
+        <v>166.07</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B165" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C165" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D165" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="4" t="s">
+      <c r="E165" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F164" s="10">
-        <v>1</v>
-      </c>
-      <c r="G164" s="4" t="s">
+      <c r="F165" s="10">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H165" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H164" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I164" s="32">
-        <v>7.2333333333333333E-2</v>
-      </c>
-      <c r="J164" s="32">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
+      <c r="I165" s="19">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J165" s="18">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D165" s="5"/>
-      <c r="E165" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F165" s="10">
-        <v>1</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H165" s="4"/>
-      <c r="I165" s="19">
-        <v>2</v>
-      </c>
-      <c r="J165" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="B166" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="F166" s="10">
         <v>1</v>
       </c>
-      <c r="G166" s="4" t="s">
-        <v>110</v>
+      <c r="G166" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H166" s="4"/>
-      <c r="I166" s="19">
-        <v>2.7678333333333334</v>
-      </c>
-      <c r="J166" s="18">
-        <v>166.07</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I166" s="29">
+        <v>3.5666666666666666E-2</v>
+      </c>
+      <c r="J166" s="29">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D167" s="26" t="s">
-        <v>104</v>
-      </c>
+      <c r="B167" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D167" s="5"/>
       <c r="E167" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F167" s="10">
         <v>1</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H167" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="G167" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H167" s="4"/>
       <c r="I167" s="19">
-        <v>7.3499999999999996E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="J167" s="18">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
+      </c>
+      <c r="B168" s="26" t="s">
+        <v>103</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D168" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F168" s="10">
+        <v>1</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H168" s="4"/>
+      <c r="I168" s="19">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="J168" s="18">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D169" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E168" s="4" t="s">
+      <c r="E169" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F168" s="10">
-        <v>1</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H168" s="4"/>
-      <c r="I168" s="32">
-        <v>3.5666666666666666E-2</v>
-      </c>
-      <c r="J168" s="32">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
+      <c r="F169" s="10">
+        <v>1</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H169" s="4"/>
+      <c r="I169" s="29">
+        <v>7.85E-2</v>
+      </c>
+      <c r="J169" s="29">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B169" s="14" t="s">
+      <c r="B170" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C170" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D169" s="5"/>
-      <c r="E169" s="4" t="s">
+      <c r="D170" s="5"/>
+      <c r="E170" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F169" s="10">
-        <v>1</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H169" s="4"/>
-      <c r="I169" s="19">
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="J169" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B170" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F170" s="10">
         <v>1</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="H170" s="4"/>
       <c r="I170" s="19">
-        <v>6.0499999999999998E-2</v>
+        <v>0.128</v>
       </c>
       <c r="J170" s="18">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="F171" s="10">
         <v>1</v>
       </c>
-      <c r="G171" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H171" s="4"/>
-      <c r="I171" s="32">
-        <v>7.85E-2</v>
-      </c>
-      <c r="J171" s="32">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G171" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I171" s="19">
+        <v>7.3499999999999996E-2</v>
+      </c>
+      <c r="J171" s="18">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D172" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="E172" s="4" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F172" s="10">
         <v>1</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H172" s="4"/>
       <c r="I172" s="19">
-        <v>0.128</v>
+        <v>3.5666666666666666E-2</v>
       </c>
       <c r="J172" s="18">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="F173" s="10">
         <v>1</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H173" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I173" s="19">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="J173" s="18">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+      <c r="H173" s="4"/>
+      <c r="I173" s="29">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J173" s="29">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
       <c r="B174" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D174" s="5"/>
+      <c r="E174" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F174" s="10">
+        <v>1</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I174" s="19">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="J174" s="18">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B175" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F174" s="10">
-        <v>1</v>
-      </c>
-      <c r="G174" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H174" s="4"/>
-      <c r="I174" s="19">
-        <v>3.5666666666666666E-2</v>
-      </c>
-      <c r="J174" s="18">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D175" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E175" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F175" s="10">
+        <v>1</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H175" s="4"/>
+      <c r="I175" s="19">
+        <v>7.85E-2</v>
+      </c>
+      <c r="J175" s="18">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D176" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E175" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F175" s="10">
-        <v>1</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H175" s="4"/>
-      <c r="I175" s="32">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J175" s="32">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D176" s="5"/>
-      <c r="E176" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F176" s="10">
         <v>1</v>
       </c>
-      <c r="G176" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H176" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I176" s="19">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="J176" s="18">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G176" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H176" s="4"/>
+      <c r="I176" s="29">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J176" s="29">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D177" s="5"/>
       <c r="E177" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F177" s="10">
         <v>1</v>
       </c>
-      <c r="G177" s="4" t="s">
-        <v>256</v>
+      <c r="G177" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H177" s="4"/>
       <c r="I177" s="19">
-        <v>7.85E-2</v>
+        <v>3</v>
       </c>
       <c r="J177" s="18">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>99</v>
+        <v>54</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="F178" s="10">
         <v>1</v>
       </c>
-      <c r="G178" s="3" t="s">
-        <v>256</v>
+      <c r="G178" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="H178" s="4"/>
-      <c r="I178" s="32">
-        <v>5.1833333333333328E-2</v>
-      </c>
-      <c r="J178" s="32">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I178" s="19">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J178" s="18">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D179" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="E179" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F179" s="10">
         <v>1</v>
       </c>
-      <c r="G179" s="3" t="s">
-        <v>256</v>
+      <c r="G179" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="H179" s="4"/>
       <c r="I179" s="19">
-        <v>3</v>
+        <v>1.6333333333333333</v>
       </c>
       <c r="J179" s="18">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>103</v>
@@ -6664,29 +6643,29 @@
       <c r="F180" s="10">
         <v>1</v>
       </c>
-      <c r="G180" s="4" t="s">
-        <v>256</v>
+      <c r="G180" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H180" s="4"/>
       <c r="I180" s="19">
-        <v>0.10483333333333333</v>
+        <v>3.7666666666666661E-2</v>
       </c>
       <c r="J180" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>109</v>
+        <v>65</v>
+      </c>
+      <c r="D181" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>64</v>
@@ -6697,149 +6676,147 @@
       <c r="G181" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H181" s="4"/>
+      <c r="H181" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="I181" s="19">
-        <v>1.6333333333333333</v>
+        <v>7.2333333333333333E-2</v>
       </c>
       <c r="J181" s="18">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="C182" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D182" s="5"/>
       <c r="E182" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F182" s="10">
         <v>1</v>
       </c>
-      <c r="G182" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H182" s="4"/>
+      <c r="G182" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="I182" s="19">
-        <v>3.7666666666666661E-2</v>
+        <v>6.0499999999999998E-2</v>
       </c>
       <c r="J182" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" s="13" t="s">
         <v>224</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D183" s="26" t="s">
+      <c r="D183" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E183" s="4" t="s">
+      <c r="E183" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F183" s="10">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4" t="s">
+      <c r="F183" s="16">
+        <v>1</v>
+      </c>
+      <c r="G183" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H183" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H183" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="I183" s="19">
-        <v>7.2333333333333333E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="J183" s="18">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B184" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D184" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F184" s="10">
+        <v>1</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H184" s="4"/>
+      <c r="I184" s="19">
+        <v>3.5666666666666666E-2</v>
+      </c>
+      <c r="J184" s="18">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B185" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C185" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D184" s="5"/>
-      <c r="E184" s="4" t="s">
+      <c r="D185" s="5"/>
+      <c r="E185" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F184" s="10">
-        <v>1</v>
-      </c>
-      <c r="G184" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H184" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I184" s="19">
-        <v>6.0499999999999998E-2</v>
-      </c>
-      <c r="J184" s="18">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D185" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E185" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F185" s="16">
-        <v>1</v>
-      </c>
-      <c r="G185" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H185" s="15" t="s">
-        <v>110</v>
-      </c>
+      <c r="F185" s="10">
+        <v>1</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="H185" s="4"/>
       <c r="I185" s="19">
-        <v>7.3499999999999996E-2</v>
+        <v>0.128</v>
       </c>
       <c r="J185" s="18">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D186" s="26" t="s">
+      <c r="D186" s="23" t="s">
         <v>112</v>
       </c>
       <c r="E186" s="4" t="s">
@@ -6849,19 +6826,19 @@
         <v>1</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H186" s="4"/>
       <c r="I186" s="19">
-        <v>3.5666666666666666E-2</v>
+        <v>7.85E-2</v>
       </c>
       <c r="J186" s="18">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>98</v>
@@ -6877,27 +6854,29 @@
         <v>1</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H187" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="I187" s="19">
-        <v>0.128</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="J187" s="18">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B188" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="B188" s="7" t="s">
         <v>99</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D188" s="26" t="s">
+      <c r="D188" s="23" t="s">
         <v>112</v>
       </c>
       <c r="E188" s="4" t="s">
@@ -6906,26 +6885,26 @@
       <c r="F188" s="10">
         <v>1</v>
       </c>
-      <c r="G188" s="3" t="s">
-        <v>256</v>
+      <c r="G188" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" s="19">
-        <v>7.85E-2</v>
+        <v>0.10483333333333333</v>
       </c>
       <c r="J188" s="18">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B189" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B189" s="14" t="s">
         <v>98</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D189" s="5"/>
       <c r="E189" s="4" t="s">
@@ -6935,29 +6914,27 @@
         <v>1</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>256</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="H189" s="4"/>
       <c r="I189" s="19">
-        <v>7.3499999999999996E-2</v>
+        <v>3.7666666666666661E-2</v>
       </c>
       <c r="J189" s="18">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B190" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B190" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D190" s="26" t="s">
+      <c r="D190" s="23" t="s">
         <v>112</v>
       </c>
       <c r="E190" s="4" t="s">
@@ -6966,106 +6943,108 @@
       <c r="F190" s="10">
         <v>1</v>
       </c>
-      <c r="G190" s="4" t="s">
-        <v>256</v>
+      <c r="G190" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H190" s="4"/>
       <c r="I190" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J190" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J190" s="9">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B191" s="14" t="s">
-        <v>98</v>
+        <v>186</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D191" s="5"/>
       <c r="E191" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F191" s="10">
         <v>1</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H191" s="4"/>
       <c r="I191" s="19">
-        <v>3.7666666666666661E-2</v>
+        <v>6</v>
       </c>
       <c r="J191" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D192" s="26" t="s">
-        <v>112</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D192" s="5"/>
       <c r="E192" s="4" t="s">
         <v>64</v>
       </c>
       <c r="F192" s="10">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H192" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>254</v>
+      </c>
       <c r="I192" s="19">
-        <v>5.1833333333333328E-2</v>
-      </c>
-      <c r="J192" s="9">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.2333333333333333E-2</v>
+      </c>
+      <c r="J192" s="18">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B193" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B193" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E193" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C193" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D193" s="5"/>
-      <c r="E193" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="F193" s="10">
         <v>1</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="19">
-        <v>6</v>
+        <v>1.2273333333333334</v>
       </c>
       <c r="J193" s="18">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>73.64</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>113</v>
@@ -7075,16 +7054,16 @@
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F194" s="10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I194" s="19">
         <v>7.2333333333333333E-2</v>
@@ -7093,18 +7072,18 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B195" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B195" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>253</v>
+      <c r="D195" t="s">
+        <v>252</v>
       </c>
       <c r="E195" s="4" t="s">
         <v>83</v>
@@ -7117,15 +7096,15 @@
       </c>
       <c r="H195" s="4"/>
       <c r="I195" s="19">
-        <v>1.2273333333333334</v>
+        <v>2.2166666666666668</v>
       </c>
       <c r="J195" s="18">
-        <v>73.64</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>174</v>
+        <v>230</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>113</v>
@@ -7135,36 +7114,36 @@
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F196" s="10">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I196" s="19">
-        <v>7.2333333333333333E-2</v>
+        <v>6.3166666666666663E-2</v>
       </c>
       <c r="J196" s="18">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D197" t="s">
-        <v>254</v>
+        <v>65</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>83</v>
@@ -7172,20 +7151,20 @@
       <c r="F197" s="10">
         <v>1</v>
       </c>
-      <c r="G197" s="4" t="s">
-        <v>68</v>
+      <c r="G197" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H197" s="4"/>
       <c r="I197" s="19">
-        <v>2.2166666666666668</v>
+        <v>3.7666666666666661E-2</v>
       </c>
       <c r="J197" s="18">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>113</v>
@@ -7195,16 +7174,16 @@
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F198" s="10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I198" s="19">
         <v>6.3166666666666663E-2</v>
@@ -7213,18 +7192,18 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>255</v>
+        <v>92</v>
       </c>
       <c r="E199" s="4" t="s">
         <v>83</v>
@@ -7232,20 +7211,20 @@
       <c r="F199" s="10">
         <v>1</v>
       </c>
-      <c r="G199" s="3" t="s">
-        <v>256</v>
+      <c r="G199" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="H199" s="4"/>
       <c r="I199" s="19">
-        <v>3.7666666666666661E-2</v>
+        <v>1.6833333333333333</v>
       </c>
       <c r="J199" s="18">
-        <v>2.2599999999999998</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>113</v>
@@ -7261,30 +7240,30 @@
         <v>0.6</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I200" s="19">
-        <v>6.3166666666666663E-2</v>
+        <v>0.128</v>
       </c>
       <c r="J200" s="18">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>118</v>
+        <v>232</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E201" s="4" t="s">
         <v>83</v>
@@ -7295,15 +7274,17 @@
       <c r="G201" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H201" s="4"/>
+      <c r="H201" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="I201" s="19">
-        <v>1.6833333333333333</v>
-      </c>
-      <c r="J201" s="18">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J201" s="9">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>233</v>
       </c>
@@ -7315,27 +7296,25 @@
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="4" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="F202" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>256</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="H202" s="4"/>
       <c r="I202" s="19">
-        <v>0.128</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J202" s="18">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>234</v>
+        <v>61</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>82</v>
@@ -7344,30 +7323,30 @@
         <v>53</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E203" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E203" s="3" t="s">
         <v>83</v>
       </c>
       <c r="F203" s="10">
         <v>1</v>
       </c>
-      <c r="G203" s="4" t="s">
+      <c r="G203" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H203" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H203" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="I203" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J203" s="9">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="J203" s="18">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>113</v>
@@ -7383,19 +7362,19 @@
         <v>1</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="19">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="J204" s="18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="J204" s="9">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>82</v>
@@ -7404,36 +7383,34 @@
         <v>53</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E205" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E205" s="4" t="s">
         <v>83</v>
       </c>
       <c r="F205" s="10">
         <v>1</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H205" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="H205" s="4"/>
       <c r="I205" s="19">
-        <v>5.0499999999999996E-2</v>
+        <v>2.8333333333333332E-2</v>
       </c>
       <c r="J205" s="18">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>113</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="4" t="s">
@@ -7443,47 +7420,45 @@
         <v>1</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H206" s="4"/>
       <c r="I206" s="19">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="J206" s="9">
-        <v>4.62</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
-        <v>115</v>
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="J206" s="18">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" s="28" t="s">
+        <v>236</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D207" s="5"/>
       <c r="E207" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F207" s="10">
         <v>1</v>
       </c>
-      <c r="G207" s="3" t="s">
-        <v>256</v>
+      <c r="G207" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="H207" s="4"/>
       <c r="I207" s="19">
-        <v>2.8333333333333332E-2</v>
+        <v>7.9333333333333325E-2</v>
       </c>
       <c r="J207" s="18">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>237</v>
       </c>
@@ -7501,55 +7476,57 @@
         <v>1</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" s="19">
-        <v>5.9499999999999997E-2</v>
-      </c>
-      <c r="J208" s="18">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="31" t="s">
-        <v>238</v>
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J208" s="9">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="4" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="F209" s="10">
         <v>1</v>
       </c>
-      <c r="G209" s="4" t="s">
-        <v>125</v>
+      <c r="G209" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" s="19">
-        <v>7.9333333333333325E-2</v>
-      </c>
-      <c r="J209" s="18">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="J209" s="9">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>239</v>
+        <v>60</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D210" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="E210" s="4" t="s">
         <v>114</v>
       </c>
@@ -7557,19 +7534,21 @@
         <v>1</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H210" s="4"/>
+        <v>254</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I210" s="19">
-        <v>5.1833333333333328E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J210" s="9">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>83</v>
@@ -7585,22 +7564,22 @@
         <v>1</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H211" s="4"/>
       <c r="I211" s="19">
-        <v>6</v>
-      </c>
-      <c r="J211" s="9">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="J211" s="18">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>56</v>
@@ -7615,17 +7594,19 @@
         <v>1</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>68</v>
       </c>
       <c r="I212" s="19">
-        <v>0</v>
-      </c>
-      <c r="J212" s="9"/>
-    </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.0499999999999996E-2</v>
+      </c>
+      <c r="J212" s="9">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>209</v>
       </c>
@@ -7643,28 +7624,28 @@
         <v>1</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H213" s="4"/>
       <c r="I213" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J213" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>92</v>
+        <v>251</v>
       </c>
       <c r="E214" s="4" t="s">
         <v>114</v>
@@ -7673,19 +7654,19 @@
         <v>1</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H214" s="4" t="s">
         <v>68</v>
       </c>
+      <c r="H214" s="4"/>
       <c r="I214" s="19">
-        <v>0</v>
-      </c>
-      <c r="J214" s="9"/>
-    </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.2273333333333334</v>
+      </c>
+      <c r="J214" s="9">
+        <v>73.64</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>83</v>
@@ -7701,19 +7682,19 @@
         <v>1</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H215" s="4"/>
-      <c r="I215" s="19">
-        <v>1</v>
+      <c r="I215" s="25">
+        <v>2</v>
       </c>
       <c r="J215" s="18">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>99</v>
@@ -7722,7 +7703,7 @@
         <v>56</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E216" s="4" t="s">
         <v>114</v>
@@ -7735,52 +7716,52 @@
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="19">
-        <v>1.2273333333333334</v>
-      </c>
-      <c r="J216" s="9">
-        <v>73.64</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2.2166666666666668</v>
+      </c>
+      <c r="J216" s="18">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>83</v>
+        <v>239</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D217" s="5"/>
       <c r="E217" s="4" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F217" s="10">
         <v>1</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H217" s="4"/>
-      <c r="I217" s="28">
-        <v>2</v>
+      <c r="I217" s="19">
+        <v>0.10483333333333333</v>
       </c>
       <c r="J217" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>254</v>
+        <v>92</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>114</v>
@@ -7793,53 +7774,51 @@
       </c>
       <c r="H218" s="4"/>
       <c r="I218" s="19">
-        <v>2.2166666666666668</v>
-      </c>
-      <c r="J218" s="18">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.6833333333333333</v>
+      </c>
+      <c r="J218" s="9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>47</v>
+        <v>210</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F219" s="10">
         <v>1</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H219" s="4"/>
       <c r="I219" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J219" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="J219" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D220" s="5" t="s">
-        <v>92</v>
-      </c>
+      <c r="D220" s="5"/>
       <c r="E220" s="4" t="s">
         <v>114</v>
       </c>
@@ -7847,17 +7826,21 @@
         <v>1</v>
       </c>
       <c r="G220" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H220" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H220" s="4"/>
       <c r="I220" s="19">
-        <v>0</v>
-      </c>
-      <c r="J220" s="9"/>
-    </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="J220" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>83</v>
@@ -7873,189 +7856,191 @@
         <v>1</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H221" s="4"/>
       <c r="I221" s="19">
-        <v>2</v>
-      </c>
-      <c r="J221" s="9">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+      <c r="J221" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D222" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>253</v>
+      </c>
       <c r="E222" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F222" s="10">
         <v>1</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H222" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="H222" s="4"/>
       <c r="I222" s="19">
-        <v>0</v>
-      </c>
-      <c r="J222" s="9"/>
-    </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.1833333333333328E-2</v>
+      </c>
+      <c r="J222" s="9">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D223" s="5"/>
       <c r="E223" s="4" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F223" s="10">
         <v>1</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H223" s="4"/>
       <c r="I223" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="J223" s="18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>185</v>
+        <v>2.8333333333333332E-2</v>
+      </c>
+      <c r="J223" s="9">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D224" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="E224" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F224" s="10">
-        <v>1</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H224" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="C224" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D224" s="5"/>
+      <c r="E224" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F224" s="16">
+        <v>1</v>
+      </c>
+      <c r="G224" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H224" s="15"/>
       <c r="I224" s="19">
-        <v>5.1833333333333328E-2</v>
+        <v>10</v>
       </c>
       <c r="J224" s="9">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D225" s="5"/>
       <c r="E225" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F225" s="10">
         <v>1</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H225" s="4"/>
       <c r="I225" s="19">
-        <v>2.8333333333333332E-2</v>
+        <v>2</v>
       </c>
       <c r="J225" s="9">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C226" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D226" s="5"/>
-      <c r="E226" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F226" s="16">
-        <v>1</v>
-      </c>
-      <c r="G226" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H226" s="15"/>
+      <c r="D226" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F226" s="10">
+        <v>1</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H226" s="4"/>
       <c r="I226" s="19">
-        <v>10</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="J226" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D227" s="5"/>
       <c r="E227" s="4" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="F227" s="10">
         <v>1</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H227" s="4"/>
       <c r="I227" s="19">
-        <v>2</v>
-      </c>
-      <c r="J227" s="9">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="J227" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>123</v>
+        <v>232</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>81</v>
@@ -8073,17 +8058,21 @@
         <v>1</v>
       </c>
       <c r="G228" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H228" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H228" s="4"/>
       <c r="I228" s="19">
-        <v>0</v>
-      </c>
-      <c r="J228" s="9"/>
-    </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J228">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>47</v>
@@ -8099,51 +8088,49 @@
         <v>1</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H229" s="4"/>
       <c r="I229" s="19">
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="J229" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.128</v>
+      </c>
+      <c r="J229" s="9">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D230" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D230" s="5"/>
       <c r="E230" s="4" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="F230" s="10">
         <v>1</v>
       </c>
-      <c r="G230" s="3" t="s">
+      <c r="G230" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H230" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="H230" s="4"/>
       <c r="I230" s="19">
-        <v>0</v>
-      </c>
-      <c r="J230" s="18"/>
-    </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="J230" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B231" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B231" t="s">
         <v>47</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -8151,27 +8138,27 @@
       </c>
       <c r="D231" s="5"/>
       <c r="E231" s="4" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F231" s="10">
         <v>1</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H231" s="4"/>
       <c r="I231" s="19">
-        <v>0.128</v>
+        <v>0.05</v>
       </c>
       <c r="J231" s="9">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B232" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B232" t="s">
         <v>49</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -8191,13 +8178,13 @@
       <c r="I232" s="19">
         <v>8.3333333333333332E-3</v>
       </c>
-      <c r="J232" s="9">
+      <c r="J232" s="18">
         <v>0.5</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="B233" t="s">
         <v>47</v>
@@ -8207,25 +8194,27 @@
       </c>
       <c r="D233" s="5"/>
       <c r="E233" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F233" s="10">
         <v>1</v>
       </c>
-      <c r="G233" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H233" s="4"/>
+      <c r="G233" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="I233" s="19">
-        <v>0.05</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="J233" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="B234" t="s">
         <v>49</v>
@@ -8247,157 +8236,153 @@
       <c r="I234" s="19">
         <v>8.3333333333333332E-3</v>
       </c>
-      <c r="J234" s="18">
+      <c r="J234" s="9">
         <v>0.5</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>222</v>
+        <v>52</v>
       </c>
       <c r="B235" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D235" s="5"/>
       <c r="E235" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F235" s="10">
         <v>1</v>
       </c>
-      <c r="G235" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H235" s="3" t="s">
-        <v>256</v>
-      </c>
+      <c r="G235" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H235" s="4"/>
       <c r="I235" s="19">
-        <v>9.6000000000000002E-2</v>
+        <v>3</v>
       </c>
       <c r="J235" s="9">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>59</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A236" s="13" t="s">
+        <v>244</v>
       </c>
       <c r="B236" t="s">
         <v>49</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D236" s="5"/>
-      <c r="E236" s="4" t="s">
+      <c r="E236" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F236" s="10">
-        <v>1</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H236" s="4"/>
+      <c r="F236" s="16">
+        <v>1</v>
+      </c>
+      <c r="G236" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H236" s="15"/>
       <c r="I236" s="19">
-        <v>8.3333333333333332E-3</v>
-      </c>
-      <c r="J236" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
-        <v>52</v>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="J236" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A237" s="13" t="s">
+        <v>205</v>
       </c>
       <c r="B237" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D237" s="5"/>
-      <c r="E237" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F237" s="10">
-        <v>1</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H237" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E237" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F237" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="G237" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H237" s="15"/>
       <c r="I237" s="19">
-        <v>3</v>
+        <v>7.9333333333333325E-2</v>
       </c>
       <c r="J237" s="9">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="13" t="s">
-        <v>246</v>
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="B238" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D238" s="5"/>
-      <c r="E238" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F238" s="16">
-        <v>1</v>
-      </c>
-      <c r="G238" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H238" s="15"/>
+      <c r="E238" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F238" s="10">
+        <v>1</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H238" s="4"/>
       <c r="I238" s="19">
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="J238" s="18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J238" s="9">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B239" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D239" s="5" t="s">
+      <c r="E239" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F239" s="10">
+        <v>1</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H239" s="4"/>
+      <c r="I239" s="19">
+        <v>2</v>
+      </c>
+      <c r="J239" s="9">
         <v>120</v>
       </c>
-      <c r="E239" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F239" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="G239" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H239" s="15"/>
-      <c r="I239" s="19">
-        <v>7.9333333333333325E-2</v>
-      </c>
-      <c r="J239" s="9">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B240" t="s">
         <v>128</v>
@@ -8412,19 +8397,19 @@
         <v>1</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H240" s="4"/>
       <c r="I240" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J240" s="9">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="B241" t="s">
         <v>128</v>
@@ -8439,73 +8424,73 @@
         <v>1</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H241" s="4"/>
       <c r="I241" s="19">
         <v>2</v>
       </c>
-      <c r="J241" s="9">
+      <c r="J241" s="18">
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
-        <v>211</v>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A242" s="13" t="s">
+        <v>246</v>
       </c>
       <c r="B242" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E242" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F242" s="10">
-        <v>1</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H242" s="4"/>
+      <c r="E242" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F242" s="16">
+        <v>1</v>
+      </c>
+      <c r="G242" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H242" s="15"/>
       <c r="I242" s="19">
-        <v>1</v>
-      </c>
-      <c r="J242" s="9">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="2" t="s">
-        <v>247</v>
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J242" s="18">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A243" s="13" t="s">
+        <v>239</v>
       </c>
       <c r="B243" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E243" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F243" s="10">
-        <v>1</v>
-      </c>
-      <c r="G243" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H243" s="4"/>
+      <c r="E243" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F243" s="16">
+        <v>1</v>
+      </c>
+      <c r="G243" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H243" s="15"/>
       <c r="I243" s="19">
-        <v>2</v>
-      </c>
-      <c r="J243" s="18">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.10483333333333333</v>
+      </c>
+      <c r="J243" s="9">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B244" t="s">
         <v>49</v>
@@ -8520,98 +8505,98 @@
         <v>1</v>
       </c>
       <c r="G244" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H244" s="15"/>
       <c r="I244" s="19">
-        <v>0.10483333333333333</v>
-      </c>
-      <c r="J244" s="18">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="13" t="s">
-        <v>241</v>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="J244" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="B245" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E245" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F245" s="16">
-        <v>1</v>
-      </c>
-      <c r="G245" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H245" s="15"/>
+      <c r="E245" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F245" s="10">
+        <v>1</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H245" s="4"/>
       <c r="I245" s="19">
-        <v>0.10483333333333333</v>
+        <v>2</v>
       </c>
       <c r="J245" s="9">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="13" t="s">
-        <v>249</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="B246" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E246" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F246" s="16">
-        <v>1</v>
-      </c>
-      <c r="G246" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H246" s="15"/>
+      <c r="E246" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F246" s="10">
+        <v>1</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H246" s="4"/>
       <c r="I246" s="19">
-        <v>6.6666666666666666E-2</v>
+        <v>0.5</v>
       </c>
       <c r="J246" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="2" t="s">
-        <v>212</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A247" s="13" t="s">
+        <v>240</v>
       </c>
       <c r="B247" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E247" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F247" s="10">
-        <v>1</v>
-      </c>
-      <c r="G247" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H247" s="4"/>
+      <c r="E247" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F247" s="16">
+        <v>1</v>
+      </c>
+      <c r="G247" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H247" s="15"/>
       <c r="I247" s="19">
-        <v>2</v>
+        <v>2.8333333333333332E-2</v>
       </c>
       <c r="J247" s="9">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>213</v>
       </c>
@@ -8622,25 +8607,25 @@
         <v>45</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F248" s="10">
         <v>1</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H248" s="4"/>
       <c r="I248" s="19">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J248" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B249" t="s">
         <v>49</v>
@@ -8649,52 +8634,52 @@
         <v>45</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F249" s="16">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G249" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H249" s="15"/>
       <c r="I249" s="19">
-        <v>2.8333333333333332E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="J249" s="9">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="2" t="s">
-        <v>215</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A250" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="B250" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E250" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F250" s="10">
-        <v>1</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H250" s="4"/>
+      <c r="E250" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F250" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="G250" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H250" s="15"/>
       <c r="I250" s="19">
-        <v>2</v>
-      </c>
-      <c r="J250" s="9">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="J250" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="13" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="B251" t="s">
         <v>49</v>
@@ -8709,17 +8694,17 @@
         <v>0.6</v>
       </c>
       <c r="G251" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H251" s="15"/>
       <c r="I251" s="19">
-        <v>0.13333333333333333</v>
+        <v>0.128</v>
       </c>
       <c r="J251" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="13" t="s">
         <v>243</v>
       </c>
@@ -8736,19 +8721,19 @@
         <v>0.4</v>
       </c>
       <c r="G252" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H252" s="15"/>
       <c r="I252" s="19">
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="J252" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.05</v>
+      </c>
+      <c r="J252" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="13" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="B253" t="s">
         <v>49</v>
@@ -8763,19 +8748,19 @@
         <v>0.6</v>
       </c>
       <c r="G253" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H253" s="15"/>
       <c r="I253" s="19">
-        <v>0.128</v>
-      </c>
-      <c r="J253" s="9">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.05</v>
+      </c>
+      <c r="J253" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B254" t="s">
         <v>49</v>
@@ -8790,19 +8775,21 @@
         <v>0.4</v>
       </c>
       <c r="G254" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H254" s="15"/>
+        <v>125</v>
+      </c>
+      <c r="H254" s="15" t="s">
+        <v>254</v>
+      </c>
       <c r="I254" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="J254" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="13" t="s">
-        <v>245</v>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="J254" s="18">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="B255" t="s">
         <v>49</v>
@@ -8810,89 +8797,27 @@
       <c r="C255" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E255" s="15" t="s">
+      <c r="E255" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F255" s="16">
+      <c r="F255" s="10">
         <v>0.6</v>
       </c>
-      <c r="G255" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="H255" s="15"/>
-      <c r="I255" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="J255" s="18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B256" t="s">
-        <v>49</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E256" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F256" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="G256" s="14" t="s">
+      <c r="G255" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H256" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="I256" s="19">
+      <c r="H255" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I255">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="J256" s="18">
+      <c r="J255">
         <v>5.76</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B257" t="s">
-        <v>49</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E257" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F257" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G257" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H257" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I257">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="J257">
-        <v>5.76</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J257" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="Facteur Conducteur"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J255" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
